--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkEmailEventReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkEmailEventReport.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rm77\Desktop\ТЕСТ\DebugWin\DebugWin\Reports\Client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\VodovozSlot-1\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005B2ED2-C945-404D-89A2-C3094F5CA56E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600261A9-0457-4C92-A152-757C076D7894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Rows">Лист1!$A$4:$H$5</definedName>
+    <definedName name="Rows">Лист1!$A$4:$I$5</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Отчёт о событиях рассылки</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>{{item.Phone}}</t>
+  </si>
+  <si>
+    <t>Тип письма</t>
+  </si>
+  <si>
+    <t>{{item.EmailTypeString}}</t>
   </si>
 </sst>
 </file>
@@ -153,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -164,14 +170,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,7 +510,8 @@
     <col min="6" max="6" width="67.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
-    <col min="9" max="1019" width="10.6640625" style="1"/>
+    <col min="9" max="9" width="24.6640625" style="1" customWidth="1"/>
+    <col min="10" max="1019" width="10.6640625" style="1"/>
     <col min="1020" max="1020" width="14.83203125" style="2" customWidth="1"/>
     <col min="1021" max="1024" width="14.83203125" customWidth="1"/>
   </cols>
@@ -1563,6 +1576,9 @@
       <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="I3" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:1019" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
@@ -1588,6 +1604,9 @@
       </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1019" ht="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
